--- a/data/obx_xlsx/ATEA.OL.xlsx
+++ b/data/obx_xlsx/ATEA.OL.xlsx
@@ -10727,7 +10727,9 @@
       <c r="R25" s="15">
         <v>194.5</v>
       </c>
-      <c r="S25" s="14"/>
+      <c r="S25" s="15">
+        <v>544.4</v>
+      </c>
       <c r="T25" s="15">
         <v>383.9</v>
       </c>

--- a/data/obx_xlsx/ATEA.OL.xlsx
+++ b/data/obx_xlsx/ATEA.OL.xlsx
@@ -13971,27 +13971,13 @@
       <c r="F93" s="14"/>
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
-      <c r="I93" s="15">
-        <v>224.0</v>
-      </c>
-      <c r="J93" s="15">
-        <v>903.0</v>
-      </c>
-      <c r="K93" s="15">
-        <v>152.0</v>
-      </c>
-      <c r="L93" s="15">
-        <v>197.0</v>
-      </c>
-      <c r="M93" s="15">
-        <v>291.2</v>
-      </c>
-      <c r="N93" s="15">
-        <v>146.2</v>
-      </c>
-      <c r="O93" s="19">
-        <v>66.5</v>
-      </c>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="15"/>
+      <c r="M93" s="15"/>
+      <c r="N93" s="15"/>
+      <c r="O93" s="19"/>
       <c r="P93" s="15">
         <v>218.2</v>
       </c>
